--- a/dcf/CRWD.xlsx
+++ b/dcf/CRWD.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1104,25 +1104,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.07480948987356142</v>
+        <v>0.07482850405579983</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.07980948987356143</v>
+        <v>0.07982850405579983</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.08480948987356142</v>
+        <v>0.08482850405579982</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.08980948987356142</v>
+        <v>0.08982850405579983</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.09480948987356143</v>
+        <v>0.09482850405579983</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.09980948987356142</v>
+        <v>0.09982850405579982</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.1048094898735614</v>
+        <v>0.1048285040557998</v>
       </c>
     </row>
     <row r="5">
@@ -1130,25 +1130,25 @@
         <v>13.6</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>121.0676738751556</v>
+        <v>104.1880502447864</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>116.6587934940596</v>
+        <v>100.5207622256062</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>112.462374148259</v>
+        <v>97.02978434299136</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>108.4671559031534</v>
+        <v>93.70578277303068</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>104.662526280586</v>
+        <v>90.5399600736507</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>101.0384802108143</v>
+        <v>87.52402201918976</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>97.58558263222565</v>
+        <v>84.65014662714381</v>
       </c>
     </row>
     <row r="6">
@@ -1156,25 +1156,25 @@
         <v>14.6</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>127.2028704873602</v>
+        <v>109.2644934011211</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>122.5157501324152</v>
+        <v>105.3669853669901</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>118.0549083764983</v>
+        <v>101.6572201369989</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>113.808340091334</v>
+        <v>98.12524732369738</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>109.7647309476922</v>
+        <v>94.76168878196755</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>105.9134146646443</v>
+        <v>91.55770320748213</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>102.244333086331</v>
+        <v>88.50495307606489</v>
       </c>
     </row>
     <row r="7">
@@ -1182,25 +1182,25 @@
         <v>15.6</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>133.3380670995649</v>
+        <v>114.3409365574558</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>128.3727067707708</v>
+        <v>110.2132085083741</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>123.6474426047377</v>
+        <v>106.2846559310065</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>119.1495242795145</v>
+        <v>102.5447118743641</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>114.8669356147983</v>
+        <v>98.98341749028438</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>110.7883491184742</v>
+        <v>95.59138439577448</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>106.9030835404363</v>
+        <v>92.35975952498595</v>
       </c>
     </row>
     <row r="8">
@@ -1208,25 +1208,25 @@
         <v>16.6</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>139.4732637117696</v>
+        <v>119.4173797137906</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>134.2296634091265</v>
+        <v>115.059431649758</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>129.239976832977</v>
+        <v>110.912091725014</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>124.490708467695</v>
+        <v>106.9641764250308</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>119.9691402819044</v>
+        <v>103.2051461986012</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>115.6632835723042</v>
+        <v>99.62506558406685</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>111.5618339945416</v>
+        <v>96.21456597390703</v>
       </c>
     </row>
     <row r="9">
@@ -1234,25 +1234,25 @@
         <v>17.6</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>145.6084603239743</v>
+        <v>124.4938228701253</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>140.0866200474821</v>
+        <v>119.905654791142</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>134.8325110612163</v>
+        <v>115.5395275190216</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>129.8318926558756</v>
+        <v>111.3836409756975</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>125.0713449490106</v>
+        <v>107.4268749069181</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>120.5382180261341</v>
+        <v>103.6587467723592</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>116.2205844486469</v>
+        <v>100.0693724228281</v>
       </c>
     </row>
     <row r="10">
@@ -1260,25 +1260,25 @@
         <v>18.6</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>151.743656936179</v>
+        <v>129.57026602646</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>145.9435766858377</v>
+        <v>124.7518779325259</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>140.4250452894557</v>
+        <v>120.1669633130292</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>135.1730768440561</v>
+        <v>115.8031055263642</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>130.1735496161168</v>
+        <v>111.6486036152349</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>125.4131524799641</v>
+        <v>107.6924279606516</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>120.8793349027522</v>
+        <v>103.9241788717492</v>
       </c>
     </row>
     <row r="11">
@@ -1286,25 +1286,25 @@
         <v>19.6</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>157.8788535483837</v>
+        <v>134.6467091827947</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>151.8005333241934</v>
+        <v>129.5981010739098</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>146.017579517695</v>
+        <v>124.7943991070367</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>140.5142610322366</v>
+        <v>120.2225700770309</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>135.2757542832229</v>
+        <v>115.8703323235518</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>130.2880869337941</v>
+        <v>111.7261091489439</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>125.5380853568575</v>
+        <v>107.7789853206702</v>
       </c>
     </row>
     <row r="13">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>193.9799957275391</v>
+        <v>198.2799987792969</v>
       </c>
     </row>
     <row r="14">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.08980948987356142</v>
+        <v>0.08982850405579983</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>16.6</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.6780480569656532</v>
+        <v>0.6871489513866252</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24409,7 +24409,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>193.9799957275391</v>
+        <v>198.2799987792969</v>
       </c>
     </row>
     <row r="49">
@@ -24419,7 +24419,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24571,13 +24571,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>124.490708467695</v>
+        <v>106.9641764250308</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>171.4808382326526</v>
+        <v>143.373345277046</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>89.73454767548134</v>
+        <v>79.29951826697459</v>
       </c>
     </row>
     <row r="59">
